--- a/Codelist Excel Files and Conversion Templates to XML/grp-aashtoM145.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/grp-aashtoM145.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10719"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/Documents/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18519A5-5F01-3742-A626-5BBB1FE29145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16067AD-DC3F-674A-8C24-F50DB902C756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10940" yWindow="4180" windowWidth="35840" windowHeight="20760" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -827,7 +827,7 @@
     <t>Fine beach sand or fine desert blow sand without silty or clay fines or with a very small amount of nonplastic silt. The group includes also stream-deposited mixtures of poorly graded fine sand and limited amounts of coarse sand and gravel.</t>
   </si>
   <si>
-    <t>//diggs:Lithology/diggs:classificationSymbol</t>
+    <t>//diggs:LithologyObservation//diggs:classificationSymbol</t>
   </si>
 </sst>
 </file>
@@ -1026,59 +1026,6 @@
   </cellStyles>
   <dxfs count="21">
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1215,6 +1162,59 @@
       </font>
       <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium7"/>
   <extLst>
@@ -1229,47 +1229,47 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DictionaryName" displayName="DictionaryName" ref="A1:E3" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DictionaryName" displayName="DictionaryName" ref="A1:E3" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="A1:E3" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Start" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Dictionary ID" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="DictionaryFile" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DictionaryName" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Start" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Dictionary ID" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="DictionaryFile" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DictionaryName" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:H9" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:H9" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="A1:H9" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Start" dataDxfId="11">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Start" dataDxfId="7">
       <calculatedColumnFormula>IF(ISNA(VLOOKUP(B2,AssociatedElements!B$2:B2831,1,FALSE)),"Not used","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="ID" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Name" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="DataType" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="QuantityClass" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Authority" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Reference" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="ID" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Name" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="DataType" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="QuantityClass" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Authority" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Reference" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AssociatedElements" displayName="AssociatedElements" ref="A1:D9" totalsRowShown="0" headerRowDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AssociatedElements" displayName="AssociatedElements" ref="A1:D9" totalsRowShown="0" headerRowDxfId="20">
   <autoFilter ref="A1:D9" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Start" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Start" dataDxfId="19">
       <calculatedColumnFormula>IF(ISNA(VLOOKUP(B2,Definitions!B$2:B$1819,1,FALSE)),"Not listed","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="ID" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="SourceElement" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="ID" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="SourceElement" dataDxfId="17"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="ConditionalElement"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
